--- a/Shared/XLS/Craft.xlsx
+++ b/Shared/XLS/Craft.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675"/>
   </bookViews>
   <sheets>
     <sheet name="#ItemEnhance" sheetId="2" r:id="rId1"/>
@@ -809,7 +809,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Craft.xlsx
+++ b/Shared/XLS/Craft.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#ItemEnhance" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="62">
   <si>
     <t>Weapon</t>
   </si>
@@ -119,10 +119,6 @@
     <t>Amulet</t>
   </si>
   <si>
-    <t>ItemPromotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>!EnumTable</t>
   </si>
   <si>
@@ -174,21 +170,7 @@
     <t>AccessoryScroll</t>
   </si>
   <si>
-    <t>ReqCurrency_2</t>
-  </si>
-  <si>
-    <t>ReqCost_2</t>
-  </si>
-  <si>
     <t>!Currency</t>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReqCurrency_2</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ReqCost_2</t>
@@ -204,10 +186,6 @@
   </si>
   <si>
     <t>TransferStone</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemEnhance</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -289,10 +267,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>ReqGoldCount</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>ItemTransfer</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -302,6 +276,38 @@
   </si>
   <si>
     <t>ReqCost</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReqMainCurrency</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReqMainCost</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReqCost_2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemEnhance</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemPromotion</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReqCurrency_2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MagicCrystal</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -483,7 +489,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -535,6 +541,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -809,7 +821,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -817,91 +829,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="6" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="16.25" style="7" customWidth="1"/>
-    <col min="15" max="15" width="9" style="7" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="7"/>
+    <col min="9" max="9" width="14.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="16.25" style="7" customWidth="1"/>
+    <col min="16" max="16" width="9" style="7" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B1" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>57</v>
+      </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="8"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="I3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="7">
         <v>1</v>
@@ -913,20 +932,25 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F4" s="7">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="7">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="7">
+      <c r="I4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" s="7">
         <v>100</v>
       </c>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -937,21 +961,26 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F5" s="7">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="7">
         <v>50</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="I5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="7">
         <v>5000</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K5"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="7">
         <v>3</v>
@@ -963,21 +992,26 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F6" s="7">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="7">
         <v>250</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="7">
+      <c r="I6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="7">
         <v>25000</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K6"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="7">
         <v>4</v>
@@ -986,24 +1020,29 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F7" s="7">
+        <v>100</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="7">
         <v>1000</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="7">
+      <c r="I7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" s="7">
         <v>100000</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K7"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1011,24 +1050,29 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F8" s="7">
+        <v>150</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="7">
         <v>3000</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="7">
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="7">
         <v>300000</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K8"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1036,24 +1080,29 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F9" s="7">
+        <v>250</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="7">
         <v>5000</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="7">
+      <c r="I9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="7">
         <v>500000</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K9"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="7">
         <v>7</v>
       </c>
@@ -1064,21 +1113,26 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F10" s="7">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="7">
         <v>1</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="7">
+      <c r="I10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="7">
         <v>100</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K10"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -1089,21 +1143,26 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F11" s="7">
         <v>25</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>43</v>
+      <c r="G11" t="s">
+        <v>37</v>
       </c>
       <c r="H11" s="7">
-        <v>2500</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" s="7">
+        <v>5000</v>
+      </c>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -1114,21 +1173,26 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F12" s="7">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="7">
         <v>125</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="7">
-        <v>12500</v>
-      </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>56</v>
+      </c>
+      <c r="J12" s="7">
+        <v>25000</v>
+      </c>
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -1136,24 +1200,29 @@
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F13" s="7">
+        <v>100</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="7">
         <v>500</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="7">
-        <v>50000</v>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="16"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="7">
+        <v>100000</v>
+      </c>
+      <c r="K13" s="16"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -1161,23 +1230,28 @@
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F14" s="7">
+        <v>150</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="7">
         <v>1500</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="7">
-        <v>150000</v>
-      </c>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14" s="7">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -1185,23 +1259,28 @@
         <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F15" s="7">
+        <v>250</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="7">
         <v>3000</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="7">
-        <v>300000</v>
-      </c>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I15" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="7">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="7">
         <v>13</v>
       </c>
@@ -1212,20 +1291,25 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F16" s="7">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="7">
         <v>1</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" s="7">
+      <c r="I16" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="7">
         <v>100</v>
       </c>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -1236,19 +1320,25 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F17" s="7">
         <v>25</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>43</v>
+      <c r="G17" t="s">
+        <v>37</v>
       </c>
       <c r="H17" s="7">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I17" t="s">
+        <v>56</v>
+      </c>
+      <c r="J17" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -1259,19 +1349,25 @@
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F18" s="7">
+        <v>50</v>
+      </c>
+      <c r="G18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="7">
         <v>125</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="7">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I18" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="7">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -1279,22 +1375,28 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F19" s="7">
+        <v>100</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="7">
         <v>500</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="7">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I19" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -1302,22 +1404,28 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F20" s="7">
+        <v>150</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="7">
         <v>1500</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="7">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I20" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="7">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -1325,22 +1433,28 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F21" s="7">
+        <v>250</v>
+      </c>
+      <c r="G21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="7">
         <v>3000</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="7">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I21" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21" s="7">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="7">
         <v>19</v>
       </c>
@@ -1351,19 +1465,25 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F22" s="7">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="7">
         <v>1</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="7">
+      <c r="I22" t="s">
+        <v>56</v>
+      </c>
+      <c r="J22" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -1374,19 +1494,25 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F23" s="7">
         <v>25</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>43</v>
+      <c r="G23" t="s">
+        <v>37</v>
       </c>
       <c r="H23" s="7">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I23" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -1397,19 +1523,25 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F24" s="7">
+        <v>50</v>
+      </c>
+      <c r="G24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="7">
         <v>125</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="7">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I24" t="s">
+        <v>56</v>
+      </c>
+      <c r="J24" s="7">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -1417,22 +1549,28 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F25" s="7">
+        <v>100</v>
+      </c>
+      <c r="G25" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="7">
         <v>500</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="7">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I25" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" s="7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -1440,22 +1578,28 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F26" s="7">
+        <v>150</v>
+      </c>
+      <c r="G26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="7">
         <v>1500</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="7">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I26" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" s="7">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -1463,22 +1607,28 @@
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F27" s="7">
+        <v>250</v>
+      </c>
+      <c r="G27" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27" s="7">
         <v>3000</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="7">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I27" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="7">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="7">
         <v>25</v>
       </c>
@@ -1489,19 +1639,25 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F28" s="7">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" s="7">
         <v>1</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="7">
+      <c r="I28" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -1512,19 +1668,25 @@
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F29" s="7">
         <v>25</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>43</v>
+      <c r="G29" t="s">
+        <v>37</v>
       </c>
       <c r="H29" s="7">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I29" t="s">
+        <v>56</v>
+      </c>
+      <c r="J29" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -1535,19 +1697,25 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F30" s="7">
+        <v>50</v>
+      </c>
+      <c r="G30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H30" s="7">
         <v>125</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H30" s="7">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I30" t="s">
+        <v>56</v>
+      </c>
+      <c r="J30" s="7">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -1555,22 +1723,28 @@
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F31" s="7">
+        <v>100</v>
+      </c>
+      <c r="G31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H31" s="7">
         <v>500</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H31" s="7">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I31" t="s">
+        <v>56</v>
+      </c>
+      <c r="J31" s="7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -1578,22 +1752,28 @@
         <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F32" s="7">
+        <v>150</v>
+      </c>
+      <c r="G32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="7">
         <v>1500</v>
       </c>
-      <c r="G32" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H32" s="7">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J32" s="7">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -1601,22 +1781,28 @@
         <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F33" s="7">
+        <v>250</v>
+      </c>
+      <c r="G33" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="7">
         <v>3000</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H33" s="7">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I33" t="s">
+        <v>56</v>
+      </c>
+      <c r="J33" s="7">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="7">
         <v>31</v>
       </c>
@@ -1627,19 +1813,25 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F34" s="7">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="7">
         <v>1</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H34" s="7">
+      <c r="I34" t="s">
+        <v>56</v>
+      </c>
+      <c r="J34" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -1650,19 +1842,25 @@
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F35" s="7">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="7">
         <v>35</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H35" s="7">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I35" t="s">
+        <v>56</v>
+      </c>
+      <c r="J35" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -1673,19 +1871,25 @@
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F36" s="7">
+        <v>50</v>
+      </c>
+      <c r="G36" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="7">
         <v>175</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H36" s="7">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I36" t="s">
+        <v>56</v>
+      </c>
+      <c r="J36" s="7">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -1693,22 +1897,28 @@
         <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F37" s="7">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" s="7">
         <v>800</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H37" s="7">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I37" t="s">
+        <v>56</v>
+      </c>
+      <c r="J37" s="7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -1716,22 +1926,28 @@
         <v>22</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F38" s="7">
+        <v>150</v>
+      </c>
+      <c r="G38" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="7">
         <v>2000</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H38" s="7">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I38" t="s">
+        <v>56</v>
+      </c>
+      <c r="J38" s="7">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -1739,22 +1955,28 @@
         <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F39" s="7">
+        <v>250</v>
+      </c>
+      <c r="G39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" s="7">
         <v>4000</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H39" s="7">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I39" t="s">
+        <v>56</v>
+      </c>
+      <c r="J39" s="7">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="7">
         <v>37</v>
       </c>
@@ -1765,19 +1987,25 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F40" s="7">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s">
+        <v>38</v>
+      </c>
+      <c r="H40" s="7">
         <v>1</v>
       </c>
-      <c r="G40" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H40" s="7">
+      <c r="I40" t="s">
+        <v>56</v>
+      </c>
+      <c r="J40" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -1788,19 +2016,25 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F41" s="7">
+        <v>25</v>
+      </c>
+      <c r="G41" t="s">
+        <v>38</v>
+      </c>
+      <c r="H41" s="7">
         <v>35</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" s="7">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I41" t="s">
+        <v>56</v>
+      </c>
+      <c r="J41" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -1811,19 +2045,25 @@
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F42" s="7">
+        <v>50</v>
+      </c>
+      <c r="G42" t="s">
+        <v>38</v>
+      </c>
+      <c r="H42" s="7">
         <v>175</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" s="7">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I42" t="s">
+        <v>56</v>
+      </c>
+      <c r="J42" s="7">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -1831,22 +2071,28 @@
         <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F43" s="7">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
+        <v>38</v>
+      </c>
+      <c r="H43" s="7">
         <v>800</v>
       </c>
-      <c r="G43" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H43" s="7">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I43" t="s">
+        <v>56</v>
+      </c>
+      <c r="J43" s="7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -1854,22 +2100,28 @@
         <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F44" s="7">
+        <v>150</v>
+      </c>
+      <c r="G44" t="s">
+        <v>38</v>
+      </c>
+      <c r="H44" s="7">
         <v>2000</v>
       </c>
-      <c r="G44" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H44" s="7">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I44" t="s">
+        <v>56</v>
+      </c>
+      <c r="J44" s="7">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -1877,22 +2129,28 @@
         <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F45" s="7">
+        <v>250</v>
+      </c>
+      <c r="G45" t="s">
+        <v>38</v>
+      </c>
+      <c r="H45" s="7">
         <v>4000</v>
       </c>
-      <c r="G45" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H45" s="7">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I45" t="s">
+        <v>56</v>
+      </c>
+      <c r="J45" s="7">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" s="7">
         <v>43</v>
       </c>
@@ -1903,19 +2161,25 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F46" s="7">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" s="7">
         <v>1</v>
       </c>
-      <c r="G46" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H46" s="7">
+      <c r="I46" t="s">
+        <v>56</v>
+      </c>
+      <c r="J46" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -1926,19 +2190,25 @@
         <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F47" s="7">
+        <v>25</v>
+      </c>
+      <c r="G47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H47" s="7">
         <v>35</v>
       </c>
-      <c r="G47" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H47" s="7">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I47" t="s">
+        <v>56</v>
+      </c>
+      <c r="J47" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -1949,19 +2219,25 @@
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F48" s="7">
+        <v>50</v>
+      </c>
+      <c r="G48" t="s">
+        <v>38</v>
+      </c>
+      <c r="H48" s="7">
         <v>175</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H48" s="7">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I48" t="s">
+        <v>56</v>
+      </c>
+      <c r="J48" s="7">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -1969,22 +2245,28 @@
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F49" s="7">
+        <v>100</v>
+      </c>
+      <c r="G49" t="s">
+        <v>38</v>
+      </c>
+      <c r="H49" s="7">
         <v>800</v>
       </c>
-      <c r="G49" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H49" s="7">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I49" t="s">
+        <v>56</v>
+      </c>
+      <c r="J49" s="7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -1992,22 +2274,28 @@
         <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F50" s="7">
+        <v>150</v>
+      </c>
+      <c r="G50" t="s">
+        <v>38</v>
+      </c>
+      <c r="H50" s="7">
         <v>2000</v>
       </c>
-      <c r="G50" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H50" s="7">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I50" t="s">
+        <v>56</v>
+      </c>
+      <c r="J50" s="7">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -2015,19 +2303,25 @@
         <v>2</v>
       </c>
       <c r="D51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F51" s="7">
+        <v>250</v>
+      </c>
+      <c r="G51" t="s">
+        <v>38</v>
+      </c>
+      <c r="H51" s="7">
         <v>4000</v>
       </c>
-      <c r="G51" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H51" s="7">
-        <v>400000</v>
+      <c r="I51" t="s">
+        <v>56</v>
+      </c>
+      <c r="J51" s="7">
+        <v>500000</v>
       </c>
     </row>
   </sheetData>
@@ -2053,10 +2347,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -2071,16 +2365,16 @@
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>16</v>
@@ -2139,7 +2433,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>6</v>
@@ -2153,7 +2447,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>7</v>
@@ -2167,7 +2461,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>8</v>
@@ -2214,66 +2508,70 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="6" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.375" style="7" customWidth="1"/>
-    <col min="6" max="7" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="18.625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="17.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="16.25" style="7" customWidth="1"/>
-    <col min="17" max="17" width="9" style="7" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="7"/>
+    <col min="6" max="6" width="17.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="18.625" style="7" customWidth="1"/>
+    <col min="12" max="17" width="16.25" style="7" customWidth="1"/>
+    <col min="18" max="18" width="9" style="7" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B1" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="F2" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>44</v>
-      </c>
       <c r="I2" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K2" s="11"/>
-      <c r="L2"/>
-      <c r="M2" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="11"/>
+      <c r="M2"/>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2" s="8"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
         <v>15</v>
@@ -2288,28 +2586,31 @@
         <v>16</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="8"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="9"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3" s="8"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="7">
         <v>1</v>
@@ -2324,23 +2625,26 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G4" s="7">
+        <v>500</v>
+      </c>
+      <c r="H4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="7">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="7">
-        <v>500</v>
-      </c>
-      <c r="J4" s="7">
+      <c r="J4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="7">
         <v>50000</v>
       </c>
-      <c r="K4" s="12"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L4" s="12"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -2354,23 +2658,26 @@
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G5" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="7">
         <v>25</v>
       </c>
-      <c r="H5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="7">
-        <v>3000</v>
-      </c>
-      <c r="J5" s="7">
+      <c r="J5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="7">
         <v>100000</v>
       </c>
-      <c r="K5" s="12"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L5" s="12"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="7">
         <v>3</v>
@@ -2385,23 +2692,26 @@
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G6" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="7">
         <v>50</v>
       </c>
-      <c r="H6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="7">
-        <v>15000</v>
-      </c>
-      <c r="J6" s="7">
+      <c r="J6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="7">
         <v>500000</v>
       </c>
-      <c r="K6" s="12"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="7">
         <v>4</v>
@@ -2416,23 +2726,26 @@
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G7" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="7">
         <v>150</v>
       </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="7">
-        <v>70000</v>
-      </c>
-      <c r="J7" s="7">
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="7">
         <v>1500000</v>
       </c>
-      <c r="K7" s="12"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -2446,23 +2759,26 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G8" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="7">
         <v>500</v>
       </c>
-      <c r="H8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="7">
-        <v>200000</v>
-      </c>
-      <c r="J8" s="7">
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="7">
         <v>5000000</v>
       </c>
-      <c r="K8" s="12"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -2476,23 +2792,26 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G9" s="7">
+        <v>500</v>
+      </c>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="7">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="7">
-        <v>500</v>
-      </c>
-      <c r="J9" s="7">
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="7">
         <v>25000</v>
       </c>
-      <c r="K9" s="12"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B10" s="7">
         <v>7</v>
       </c>
@@ -2506,23 +2825,26 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G10" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="7">
         <v>25</v>
       </c>
-      <c r="H10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="7">
-        <v>3000</v>
-      </c>
-      <c r="J10" s="7">
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="7">
         <v>50000</v>
       </c>
-      <c r="K10" s="12"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2536,23 +2858,26 @@
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G11" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="7">
         <v>50</v>
       </c>
-      <c r="H11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="7">
-        <v>15000</v>
-      </c>
-      <c r="J11" s="7">
+      <c r="J11" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="7">
         <v>250000</v>
       </c>
-      <c r="K11" s="12"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L11" s="12"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2566,23 +2891,26 @@
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G12" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="7">
         <v>150</v>
       </c>
-      <c r="H12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="7">
-        <v>70000</v>
-      </c>
-      <c r="J12" s="7">
+      <c r="J12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="7">
         <v>750000</v>
       </c>
-      <c r="K12" s="12"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2596,23 +2924,26 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G13" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="7">
         <v>500</v>
       </c>
-      <c r="H13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="7">
-        <v>200000</v>
-      </c>
-      <c r="J13" s="7">
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="7">
         <v>2500000</v>
       </c>
-      <c r="K13" s="12"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2626,23 +2957,26 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G14" s="7">
+        <v>500</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="7">
         <v>10</v>
       </c>
-      <c r="H14" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" s="7">
-        <v>500</v>
-      </c>
-      <c r="J14" s="7">
+      <c r="J14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" s="7">
         <v>25000</v>
       </c>
-      <c r="K14" s="12"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L14" s="12"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2656,23 +2990,26 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G15" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" s="7">
         <v>25</v>
       </c>
-      <c r="H15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="7">
-        <v>3000</v>
-      </c>
-      <c r="J15" s="7">
+      <c r="J15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="7">
         <v>50000</v>
       </c>
-      <c r="K15" s="12"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L15" s="12"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B16" s="7">
         <v>13</v>
       </c>
@@ -2686,23 +3023,26 @@
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G16" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="7">
         <v>50</v>
       </c>
-      <c r="H16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" s="7">
-        <v>15000</v>
-      </c>
-      <c r="J16" s="7">
+      <c r="J16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="7">
         <v>250000</v>
       </c>
-      <c r="K16" s="12"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2716,22 +3056,25 @@
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G17" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H17" t="s">
+        <v>41</v>
+      </c>
+      <c r="I17" s="7">
         <v>150</v>
       </c>
-      <c r="H17" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="7">
-        <v>70000</v>
-      </c>
-      <c r="J17" s="7">
+      <c r="J17" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="7">
         <v>750000</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2745,22 +3088,25 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G18" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" s="7">
         <v>500</v>
       </c>
-      <c r="H18" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" s="7">
-        <v>200000</v>
-      </c>
-      <c r="J18" s="7">
+      <c r="J18" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" s="7">
         <v>2500000</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2774,22 +3120,25 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G19" s="7">
+        <v>500</v>
+      </c>
+      <c r="H19" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" s="7">
         <v>10</v>
       </c>
-      <c r="H19" t="s">
-        <v>47</v>
-      </c>
-      <c r="I19" s="7">
-        <v>500</v>
-      </c>
-      <c r="J19" s="7">
+      <c r="J19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" s="7">
         <v>25000</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2803,22 +3152,25 @@
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G20" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="7">
         <v>25</v>
       </c>
-      <c r="H20" t="s">
-        <v>47</v>
-      </c>
-      <c r="I20" s="7">
-        <v>3000</v>
-      </c>
-      <c r="J20" s="7">
+      <c r="J20" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="7">
         <v>50000</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2832,22 +3184,25 @@
         <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G21" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="7">
         <v>50</v>
       </c>
-      <c r="H21" t="s">
-        <v>47</v>
-      </c>
-      <c r="I21" s="7">
-        <v>15000</v>
-      </c>
-      <c r="J21" s="7">
+      <c r="J21" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21" s="7">
         <v>250000</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="7">
         <v>19</v>
       </c>
@@ -2861,22 +3216,25 @@
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G22" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="7">
         <v>150</v>
       </c>
-      <c r="H22" t="s">
-        <v>47</v>
-      </c>
-      <c r="I22" s="7">
-        <v>70000</v>
-      </c>
-      <c r="J22" s="7">
+      <c r="J22" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="7">
         <v>750000</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2890,22 +3248,25 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G23" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H23" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" s="7">
         <v>500</v>
       </c>
-      <c r="H23" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="7">
-        <v>200000</v>
-      </c>
-      <c r="J23" s="7">
+      <c r="J23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23" s="7">
         <v>2500000</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2919,22 +3280,25 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G24" s="7">
+        <v>500</v>
+      </c>
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="7">
         <v>10</v>
       </c>
-      <c r="H24" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="7">
-        <v>500</v>
-      </c>
-      <c r="J24" s="7">
+      <c r="J24" t="s">
+        <v>56</v>
+      </c>
+      <c r="K24" s="7">
         <v>25000</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2948,22 +3312,25 @@
         <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G25" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H25" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="7">
         <v>25</v>
       </c>
-      <c r="H25" t="s">
-        <v>47</v>
-      </c>
-      <c r="I25" s="7">
-        <v>3000</v>
-      </c>
-      <c r="J25" s="7">
+      <c r="J25" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="7">
         <v>50000</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -2977,22 +3344,25 @@
         <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G26" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H26" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="7">
         <v>50</v>
       </c>
-      <c r="H26" t="s">
-        <v>47</v>
-      </c>
-      <c r="I26" s="7">
-        <v>15000</v>
-      </c>
-      <c r="J26" s="7">
+      <c r="J26" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" s="7">
         <v>250000</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3006,22 +3376,25 @@
         <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G27" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="7">
         <v>150</v>
       </c>
-      <c r="H27" t="s">
-        <v>47</v>
-      </c>
-      <c r="I27" s="7">
-        <v>70000</v>
-      </c>
-      <c r="J27" s="7">
+      <c r="J27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K27" s="7">
         <v>750000</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="7">
         <v>25</v>
       </c>
@@ -3035,22 +3408,25 @@
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G28" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H28" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" s="7">
         <v>500</v>
       </c>
-      <c r="H28" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="7">
-        <v>200000</v>
-      </c>
-      <c r="J28" s="7">
+      <c r="J28" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" s="7">
         <v>2500000</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3064,22 +3440,25 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G29" s="7">
+        <v>500</v>
+      </c>
+      <c r="H29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" s="7">
         <v>10</v>
       </c>
-      <c r="H29" t="s">
-        <v>47</v>
-      </c>
-      <c r="I29" s="7">
-        <v>500</v>
-      </c>
-      <c r="J29" s="7">
+      <c r="J29" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" s="7">
         <v>25000</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3093,22 +3472,25 @@
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G30" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H30" t="s">
+        <v>41</v>
+      </c>
+      <c r="I30" s="7">
         <v>25</v>
       </c>
-      <c r="H30" t="s">
-        <v>47</v>
-      </c>
-      <c r="I30" s="7">
-        <v>3000</v>
-      </c>
-      <c r="J30" s="7">
+      <c r="J30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" s="7">
         <v>50000</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3122,22 +3504,25 @@
         <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G31" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H31" t="s">
+        <v>41</v>
+      </c>
+      <c r="I31" s="7">
         <v>50</v>
       </c>
-      <c r="H31" t="s">
-        <v>47</v>
-      </c>
-      <c r="I31" s="7">
-        <v>15000</v>
-      </c>
-      <c r="J31" s="7">
+      <c r="J31" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" s="7">
         <v>250000</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3151,22 +3536,25 @@
         <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G32" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H32" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" s="7">
         <v>150</v>
       </c>
-      <c r="H32" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="7">
-        <v>70000</v>
-      </c>
-      <c r="J32" s="7">
+      <c r="J32" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32" s="7">
         <v>750000</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3180,22 +3568,25 @@
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G33" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H33" t="s">
+        <v>41</v>
+      </c>
+      <c r="I33" s="7">
         <v>500</v>
       </c>
-      <c r="H33" t="s">
-        <v>47</v>
-      </c>
-      <c r="I33" s="7">
-        <v>200000</v>
-      </c>
-      <c r="J33" s="7">
+      <c r="J33" t="s">
+        <v>56</v>
+      </c>
+      <c r="K33" s="7">
         <v>2500000</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="7">
         <v>31</v>
       </c>
@@ -3209,22 +3600,25 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G34" s="7">
+        <v>500</v>
+      </c>
+      <c r="H34" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" s="7">
         <v>10</v>
       </c>
-      <c r="H34" t="s">
-        <v>47</v>
-      </c>
-      <c r="I34" s="7">
-        <v>500</v>
-      </c>
-      <c r="J34" s="7">
+      <c r="J34" t="s">
+        <v>56</v>
+      </c>
+      <c r="K34" s="7">
         <v>25000</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3238,22 +3632,25 @@
         <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G35" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I35" s="7">
         <v>25</v>
       </c>
-      <c r="H35" t="s">
-        <v>47</v>
-      </c>
-      <c r="I35" s="7">
-        <v>3000</v>
-      </c>
-      <c r="J35" s="7">
+      <c r="J35" t="s">
+        <v>56</v>
+      </c>
+      <c r="K35" s="7">
         <v>50000</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3267,22 +3664,25 @@
         <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G36" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H36" t="s">
+        <v>41</v>
+      </c>
+      <c r="I36" s="7">
         <v>50</v>
       </c>
-      <c r="H36" t="s">
-        <v>47</v>
-      </c>
-      <c r="I36" s="7">
-        <v>15000</v>
-      </c>
-      <c r="J36" s="7">
+      <c r="J36" t="s">
+        <v>56</v>
+      </c>
+      <c r="K36" s="7">
         <v>250000</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3296,22 +3696,25 @@
         <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G37" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H37" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" s="7">
         <v>150</v>
       </c>
-      <c r="H37" t="s">
-        <v>47</v>
-      </c>
-      <c r="I37" s="7">
-        <v>70000</v>
-      </c>
-      <c r="J37" s="7">
+      <c r="J37" t="s">
+        <v>56</v>
+      </c>
+      <c r="K37" s="7">
         <v>750000</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3325,22 +3728,25 @@
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G38" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H38" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" s="7">
         <v>500</v>
       </c>
-      <c r="H38" t="s">
-        <v>47</v>
-      </c>
-      <c r="I38" s="7">
-        <v>200000</v>
-      </c>
-      <c r="J38" s="7">
+      <c r="J38" t="s">
+        <v>56</v>
+      </c>
+      <c r="K38" s="7">
         <v>2500000</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3354,22 +3760,25 @@
         <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G39" s="7">
+        <v>500</v>
+      </c>
+      <c r="H39" t="s">
+        <v>41</v>
+      </c>
+      <c r="I39" s="7">
         <v>10</v>
       </c>
-      <c r="H39" t="s">
-        <v>47</v>
-      </c>
-      <c r="I39" s="7">
-        <v>500</v>
-      </c>
-      <c r="J39" s="7">
+      <c r="J39" t="s">
+        <v>56</v>
+      </c>
+      <c r="K39" s="7">
         <v>25000</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="7">
         <v>37</v>
       </c>
@@ -3383,22 +3792,25 @@
         <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G40" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H40" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="7">
         <v>25</v>
       </c>
-      <c r="H40" t="s">
-        <v>47</v>
-      </c>
-      <c r="I40" s="7">
-        <v>3000</v>
-      </c>
-      <c r="J40" s="7">
+      <c r="J40" t="s">
+        <v>56</v>
+      </c>
+      <c r="K40" s="7">
         <v>50000</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -3412,22 +3824,25 @@
         <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G41" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H41" t="s">
+        <v>41</v>
+      </c>
+      <c r="I41" s="7">
         <v>50</v>
       </c>
-      <c r="H41" t="s">
-        <v>47</v>
-      </c>
-      <c r="I41" s="7">
-        <v>15000</v>
-      </c>
-      <c r="J41" s="7">
+      <c r="J41" t="s">
+        <v>56</v>
+      </c>
+      <c r="K41" s="7">
         <v>250000</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -3441,22 +3856,25 @@
         <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G42" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H42" t="s">
+        <v>41</v>
+      </c>
+      <c r="I42" s="7">
         <v>150</v>
       </c>
-      <c r="H42" t="s">
-        <v>47</v>
-      </c>
-      <c r="I42" s="7">
-        <v>70000</v>
-      </c>
-      <c r="J42" s="7">
+      <c r="J42" t="s">
+        <v>56</v>
+      </c>
+      <c r="K42" s="7">
         <v>750000</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -3470,18 +3888,21 @@
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G43" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H43" t="s">
+        <v>41</v>
+      </c>
+      <c r="I43" s="7">
         <v>500</v>
       </c>
-      <c r="H43" t="s">
-        <v>47</v>
-      </c>
-      <c r="I43" s="7">
-        <v>200000</v>
-      </c>
-      <c r="J43" s="7">
+      <c r="J43" t="s">
+        <v>56</v>
+      </c>
+      <c r="K43" s="7">
         <v>2500000</v>
       </c>
     </row>
@@ -3512,7 +3933,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -3521,16 +3942,16 @@
         <v>13</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2"/>
@@ -3551,7 +3972,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>17</v>
@@ -3575,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -3593,7 +4014,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F5" s="7">
         <v>5</v>
@@ -3612,7 +4033,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F6" s="7">
         <v>10</v>
@@ -3631,7 +4052,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F7" s="7">
         <v>25</v>
@@ -3649,7 +4070,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F8" s="7">
         <v>50</v>
@@ -3667,7 +4088,7 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F9" s="7">
         <v>150</v>
@@ -3685,7 +4106,7 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F10" s="7">
         <v>1</v>
@@ -3703,7 +4124,7 @@
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F11" s="7">
         <v>5</v>
@@ -3721,7 +4142,7 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F12" s="7">
         <v>10</v>
@@ -3739,7 +4160,7 @@
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F13" s="7">
         <v>25</v>
@@ -3757,7 +4178,7 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F14" s="7">
         <v>50</v>
@@ -3775,7 +4196,7 @@
         <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F15" s="7">
         <v>150</v>
@@ -3793,7 +4214,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F16" s="7">
         <v>1</v>
@@ -3811,7 +4232,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F17" s="7">
         <v>5</v>
@@ -3828,7 +4249,7 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F18" s="7">
         <v>10</v>
@@ -3845,7 +4266,7 @@
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F19" s="7">
         <v>25</v>
@@ -3862,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F20" s="7">
         <v>50</v>
@@ -3879,7 +4300,7 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F21" s="7">
         <v>150</v>
@@ -3896,7 +4317,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F22" s="7">
         <v>1</v>
@@ -3913,7 +4334,7 @@
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F23" s="7">
         <v>5</v>
@@ -3930,7 +4351,7 @@
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F24" s="7">
         <v>10</v>
@@ -3947,7 +4368,7 @@
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F25" s="7">
         <v>25</v>
@@ -3964,7 +4385,7 @@
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F26" s="7">
         <v>50</v>
@@ -3981,7 +4402,7 @@
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F27" s="7">
         <v>150</v>
@@ -3998,7 +4419,7 @@
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F28" s="7">
         <v>1</v>
@@ -4015,7 +4436,7 @@
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F29" s="7">
         <v>5</v>
@@ -4032,7 +4453,7 @@
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F30" s="7">
         <v>10</v>
@@ -4049,7 +4470,7 @@
         <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F31" s="7">
         <v>25</v>
@@ -4066,7 +4487,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F32" s="7">
         <v>50</v>
@@ -4083,7 +4504,7 @@
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F33" s="7">
         <v>150</v>
@@ -4100,7 +4521,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F34" s="7">
         <v>1</v>
@@ -4117,7 +4538,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F35" s="7">
         <v>5</v>
@@ -4134,7 +4555,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F36" s="7">
         <v>10</v>
@@ -4151,7 +4572,7 @@
         <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F37" s="7">
         <v>25</v>
@@ -4168,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F38" s="7">
         <v>50</v>
@@ -4185,7 +4606,7 @@
         <v>8</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F39" s="7">
         <v>150</v>
@@ -4202,7 +4623,7 @@
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F40" s="7">
         <v>1</v>
@@ -4219,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F41" s="7">
         <v>5</v>
@@ -4236,7 +4657,7 @@
         <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F42" s="7">
         <v>10</v>
@@ -4253,7 +4674,7 @@
         <v>6</v>
       </c>
       <c r="E43" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F43" s="7">
         <v>25</v>
@@ -4270,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F44" s="7">
         <v>50</v>
@@ -4287,7 +4708,7 @@
         <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F45" s="7">
         <v>150</v>
@@ -4304,7 +4725,7 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F46" s="7">
         <v>1</v>
@@ -4321,7 +4742,7 @@
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F47" s="7">
         <v>5</v>
@@ -4338,7 +4759,7 @@
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F48" s="7">
         <v>10</v>
@@ -4355,7 +4776,7 @@
         <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F49" s="7">
         <v>25</v>
@@ -4372,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F50" s="7">
         <v>50</v>
@@ -4389,7 +4810,7 @@
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F51" s="7">
         <v>150</v>
